--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-fiabilite-identite.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-fiabilite-identite.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="87">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,10 +78,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -93,7 +93,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This code system includes all the French Identity reliabilty codes (InteropSanté).</t>
+    <t>French Identity reliabilty codes</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -626,7 +626,9 @@
       <c r="C2" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -638,7 +640,9 @@
       <c r="C3" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -650,7 +654,9 @@
       <c r="C4" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -662,7 +668,9 @@
       <c r="C5" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -674,7 +682,9 @@
       <c r="C6" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -686,7 +696,9 @@
       <c r="C7" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -698,7 +710,9 @@
       <c r="C8" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>58</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -710,7 +724,9 @@
       <c r="C9" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -722,7 +738,9 @@
       <c r="C10" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>62</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -734,7 +752,9 @@
       <c r="C11" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>64</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -746,7 +766,9 @@
       <c r="C12" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>66</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -758,7 +780,9 @@
       <c r="C13" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>68</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
@@ -770,7 +794,9 @@
       <c r="C14" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>70</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -782,7 +808,9 @@
       <c r="C15" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>72</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -794,7 +822,9 @@
       <c r="C16" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>74</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
@@ -806,7 +836,9 @@
       <c r="C17" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="D17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>76</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
@@ -818,7 +850,9 @@
       <c r="C18" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="D18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
@@ -830,7 +864,9 @@
       <c r="C19" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="D19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>80</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
@@ -842,7 +878,9 @@
       <c r="C20" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="D20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>82</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
@@ -854,7 +892,9 @@
       <c r="C21" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>84</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
@@ -866,7 +906,9 @@
       <c r="C22" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="D22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>86</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-fiabilite-identite.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-fiabilite-identite.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="87">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,10 +78,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -93,7 +93,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>French Identity reliabilty codes</t>
+    <t>This code system includes all the French Identity reliabilty codes (InteropSanté).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -626,9 +626,7 @@
       <c r="C2" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D2" t="s" s="2">
-        <v>46</v>
-      </c>
+      <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -640,9 +638,7 @@
       <c r="C3" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D3" t="s" s="2">
-        <v>48</v>
-      </c>
+      <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -654,9 +650,7 @@
       <c r="C4" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D4" t="s" s="2">
-        <v>50</v>
-      </c>
+      <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -668,9 +662,7 @@
       <c r="C5" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D5" t="s" s="2">
-        <v>52</v>
-      </c>
+      <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -682,9 +674,7 @@
       <c r="C6" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D6" t="s" s="2">
-        <v>54</v>
-      </c>
+      <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -696,9 +686,7 @@
       <c r="C7" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D7" t="s" s="2">
-        <v>56</v>
-      </c>
+      <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -710,9 +698,7 @@
       <c r="C8" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="D8" t="s" s="2">
-        <v>58</v>
-      </c>
+      <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -724,9 +710,7 @@
       <c r="C9" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D9" t="s" s="2">
-        <v>60</v>
-      </c>
+      <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -738,9 +722,7 @@
       <c r="C10" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="D10" t="s" s="2">
-        <v>62</v>
-      </c>
+      <c r="D10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -752,9 +734,7 @@
       <c r="C11" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="D11" t="s" s="2">
-        <v>64</v>
-      </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -766,9 +746,7 @@
       <c r="C12" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="D12" t="s" s="2">
-        <v>66</v>
-      </c>
+      <c r="D12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -780,9 +758,7 @@
       <c r="C13" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="D13" t="s" s="2">
-        <v>68</v>
-      </c>
+      <c r="D13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
@@ -794,9 +770,7 @@
       <c r="C14" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="D14" t="s" s="2">
-        <v>70</v>
-      </c>
+      <c r="D14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -808,9 +782,7 @@
       <c r="C15" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="D15" t="s" s="2">
-        <v>72</v>
-      </c>
+      <c r="D15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -822,9 +794,7 @@
       <c r="C16" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="D16" t="s" s="2">
-        <v>74</v>
-      </c>
+      <c r="D16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
@@ -836,9 +806,7 @@
       <c r="C17" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="D17" t="s" s="2">
-        <v>76</v>
-      </c>
+      <c r="D17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
@@ -850,9 +818,7 @@
       <c r="C18" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="D18" t="s" s="2">
-        <v>78</v>
-      </c>
+      <c r="D18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
@@ -864,9 +830,7 @@
       <c r="C19" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="D19" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="D19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
@@ -878,9 +842,7 @@
       <c r="C20" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="D20" t="s" s="2">
-        <v>82</v>
-      </c>
+      <c r="D20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
@@ -892,9 +854,7 @@
       <c r="C21" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="D21" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="D21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
@@ -906,9 +866,7 @@
       <c r="C22" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="D22" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="D22" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-fiabilite-identite.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-fiabilite-identite.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="87">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,10 +78,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -93,7 +93,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This code system includes all the French Identity reliabilty codes (InteropSanté).</t>
+    <t>French Identity reliabilty codes</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -626,7 +626,9 @@
       <c r="C2" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -638,7 +640,9 @@
       <c r="C3" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -650,7 +654,9 @@
       <c r="C4" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -662,7 +668,9 @@
       <c r="C5" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -674,7 +682,9 @@
       <c r="C6" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -686,7 +696,9 @@
       <c r="C7" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -698,7 +710,9 @@
       <c r="C8" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>58</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -710,7 +724,9 @@
       <c r="C9" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -722,7 +738,9 @@
       <c r="C10" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>62</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -734,7 +752,9 @@
       <c r="C11" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>64</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -746,7 +766,9 @@
       <c r="C12" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>66</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -758,7 +780,9 @@
       <c r="C13" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>68</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
@@ -770,7 +794,9 @@
       <c r="C14" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>70</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -782,7 +808,9 @@
       <c r="C15" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>72</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -794,7 +822,9 @@
       <c r="C16" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>74</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
@@ -806,7 +836,9 @@
       <c r="C17" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="D17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>76</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
@@ -818,7 +850,9 @@
       <c r="C18" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="D18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
@@ -830,7 +864,9 @@
       <c r="C19" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="D19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>80</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
@@ -842,7 +878,9 @@
       <c r="C20" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="D20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>82</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
@@ -854,7 +892,9 @@
       <c r="C21" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>84</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
@@ -866,7 +906,9 @@
       <c r="C22" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="D22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>86</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
